--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6803.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6803.xlsx
@@ -3309,9 +3309,18 @@
       <c r="F37" t="n">
         <v>0.75</v>
       </c>
+      <c r="I37" t="n">
+        <v>0.5625</v>
+      </c>
       <c r="K37" t="n">
         <v>0.482</v>
       </c>
+      <c r="M37" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.391</v>
+      </c>
       <c r="O37" t="n">
         <v>0.297</v>
       </c>
@@ -3327,12 +3336,12 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: D3@BORE, HEXB@HEX, LEG3@DRIVE, ORB_GRVDIA@DRIVE, Y@REF] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6803-08-08-06-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: D3@BORE, HEXB@HEX, LEG3@DRIVE, ORB_GRVDIA@DRIVE, Y@REF, THDMAJ_3@DRIVE, D1@BORE, D2@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6803-08-08-06-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6803-08-08-06-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6803-08-08-06-NWO-FG (PARTcommunity / CADENAS, D3@BORE=B3D, HEXB@HEX=C, LEG3@DRIVE=M7, ORB_GRVDIA@DRIVE=HT, Y@REF=Y; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6803-08-08-06-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6803-08-08-06-NWO-FG (PARTcommunity / CADENAS, D3@BORE=B3D, HEXB@HEX=C, LEG3@DRIVE=M7, ORB_GRVDIA@DRIVE=HT, Y@REF=Y, THDMAJ_3@DRIVE=B3THD, D1@BORE=B1D, D2@BORE=B2D; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -3366,9 +3375,18 @@
       <c r="F38" t="n">
         <v>0.875</v>
       </c>
+      <c r="I38" t="n">
+        <v>0.875</v>
+      </c>
       <c r="K38" t="n">
         <v>0.773</v>
       </c>
+      <c r="M38" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.391</v>
+      </c>
       <c r="O38" t="n">
         <v>0.484</v>
       </c>
@@ -3384,12 +3402,12 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: D3@BORE, HEXB@HEX, LEG3@DRIVE, ORB_GRVDIA@DRIVE, Y@REF] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6803-08-08-10-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: D3@BORE, HEXB@HEX, LEG3@DRIVE, ORB_GRVDIA@DRIVE, Y@REF, THDMAJ_3@DRIVE, D1@BORE, D2@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6803-08-08-10-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6803-08-08-10-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6803-08-08-10-NWO-FG (PARTcommunity / CADENAS, D3@BORE=B3D, HEXB@HEX=C, LEG3@DRIVE=M7, ORB_GRVDIA@DRIVE=HT, Y@REF=Y; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6803-08-08-10-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6803-08-08-10-NWO-FG (PARTcommunity / CADENAS, D3@BORE=B3D, HEXB@HEX=C, LEG3@DRIVE=M7, ORB_GRVDIA@DRIVE=HT, Y@REF=Y, THDMAJ_3@DRIVE=B3THD, D1@BORE=B1D, D2@BORE=B2D; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -3423,9 +3441,18 @@
       <c r="F39" t="n">
         <v>1.875</v>
       </c>
+      <c r="I39" t="n">
+        <v>1.875</v>
+      </c>
       <c r="K39" t="n">
         <v>1.756</v>
       </c>
+      <c r="M39" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1.312</v>
+      </c>
       <c r="O39" t="n">
         <v>1.312</v>
       </c>
@@ -3441,12 +3468,12 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: D3@BORE, HEXB@HEX, LEG3@DRIVE, ORB_GRVDIA@DRIVE, Y@REF] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6803-24-24-24-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: D3@BORE, HEXB@HEX, LEG3@DRIVE, ORB_GRVDIA@DRIVE, Y@REF, THDMAJ_3@DRIVE, D1@BORE, D2@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6803-24-24-24-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6803-24-24-24-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6803-24-24-24-NWO-FG (PARTcommunity / CADENAS, D3@BORE=B3D, HEXB@HEX=C, LEG3@DRIVE=M7, ORB_GRVDIA@DRIVE=HT, Y@REF=Y; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6803-24-24-24-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6803-24-24-24-NWO-FG (PARTcommunity / CADENAS, D3@BORE=B3D, HEXB@HEX=C, LEG3@DRIVE=M7, ORB_GRVDIA@DRIVE=HT, Y@REF=Y, THDMAJ_3@DRIVE=B3THD, D1@BORE=B1D, D2@BORE=B2D; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">

--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6803.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6803.xlsx
@@ -3300,6 +3300,12 @@
           <t>6803-08-08-06-NWO-FG</t>
         </is>
       </c>
+      <c r="B37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1.25</v>
+      </c>
       <c r="D37" t="n">
         <v>1.32</v>
       </c>
@@ -3309,12 +3315,24 @@
       <c r="F37" t="n">
         <v>0.75</v>
       </c>
+      <c r="G37" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.75</v>
+      </c>
       <c r="I37" t="n">
         <v>0.5625</v>
       </c>
+      <c r="J37" t="n">
+        <v>0.312</v>
+      </c>
       <c r="K37" t="n">
         <v>0.482</v>
       </c>
+      <c r="L37" t="n">
+        <v>0.083</v>
+      </c>
       <c r="M37" t="n">
         <v>0.391</v>
       </c>
@@ -3331,17 +3349,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: D3@BORE, HEXB@HEX, LEG3@DRIVE, ORB_GRVDIA@DRIVE, Y@REF, THDMAJ_3@DRIVE, D1@BORE, D2@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6803-08-08-06-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: D3@BORE, HEXB@HEX, LEG3@DRIVE, ORB_GRVDIA@DRIVE, Y@REF, THDMAJ_3@DRIVE, D1@BORE, D2@BORE, LEG1@DRIVE, LEG2@DRIVE, THDMAJ_1@DRIVE, THDMAJ_2@DRIVE, ORB_THDL@DRIVE, ORB_GRVW@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6803-08-08-06-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6803-08-08-06-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6803-08-08-06-NWO-FG (PARTcommunity / CADENAS, D3@BORE=B3D, HEXB@HEX=C, LEG3@DRIVE=M7, ORB_GRVDIA@DRIVE=HT, Y@REF=Y, THDMAJ_3@DRIVE=B3THD, D1@BORE=B1D, D2@BORE=B2D; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6803-08-08-06-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6803-08-08-06-NWO-FG (PARTcommunity / CADENAS, D3@BORE=B3D, HEXB@HEX=C, LEG3@DRIVE=M7, ORB_GRVDIA@DRIVE=HT, Y@REF=Y, THDMAJ_3@DRIVE=B3THD, D1@BORE=B1D, D2@BORE=B2D, LEG1@DRIVE=M1, LEG2@DRIVE=M2, THDMAJ_1@DRIVE=B1THD, THDMAJ_2@DRIVE=B2THD, ORB_THDL@DRIVE=A5, ORB_GRVW@DRIVE=A5; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -3366,6 +3384,12 @@
           <t>6803-08-08-10-NWO-FG</t>
         </is>
       </c>
+      <c r="B38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1.33</v>
+      </c>
       <c r="D38" t="n">
         <v>1.7</v>
       </c>
@@ -3375,12 +3399,24 @@
       <c r="F38" t="n">
         <v>0.875</v>
       </c>
+      <c r="G38" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.75</v>
+      </c>
       <c r="I38" t="n">
         <v>0.875</v>
       </c>
+      <c r="J38" t="n">
+        <v>0.391</v>
+      </c>
       <c r="K38" t="n">
         <v>0.773</v>
       </c>
+      <c r="L38" t="n">
+        <v>0.107</v>
+      </c>
       <c r="M38" t="n">
         <v>0.391</v>
       </c>
@@ -3397,17 +3433,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: D3@BORE, HEXB@HEX, LEG3@DRIVE, ORB_GRVDIA@DRIVE, Y@REF, THDMAJ_3@DRIVE, D1@BORE, D2@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6803-08-08-10-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: D3@BORE, HEXB@HEX, LEG3@DRIVE, ORB_GRVDIA@DRIVE, Y@REF, THDMAJ_3@DRIVE, D1@BORE, D2@BORE, LEG1@DRIVE, LEG2@DRIVE, THDMAJ_1@DRIVE, THDMAJ_2@DRIVE, ORB_THDL@DRIVE, ORB_GRVW@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6803-08-08-10-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6803-08-08-10-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6803-08-08-10-NWO-FG (PARTcommunity / CADENAS, D3@BORE=B3D, HEXB@HEX=C, LEG3@DRIVE=M7, ORB_GRVDIA@DRIVE=HT, Y@REF=Y, THDMAJ_3@DRIVE=B3THD, D1@BORE=B1D, D2@BORE=B2D; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6803-08-08-10-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6803-08-08-10-NWO-FG (PARTcommunity / CADENAS, D3@BORE=B3D, HEXB@HEX=C, LEG3@DRIVE=M7, ORB_GRVDIA@DRIVE=HT, Y@REF=Y, THDMAJ_3@DRIVE=B3THD, D1@BORE=B1D, D2@BORE=B2D, LEG1@DRIVE=M1, LEG2@DRIVE=M2, THDMAJ_1@DRIVE=B1THD, THDMAJ_2@DRIVE=B2THD, ORB_THDL@DRIVE=A5, ORB_GRVW@DRIVE=A5; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -3432,6 +3468,12 @@
           <t>6803-24-24-24-NWO-FG</t>
         </is>
       </c>
+      <c r="B39" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="C39" t="n">
+        <v>2.33</v>
+      </c>
       <c r="D39" t="n">
         <v>2.39</v>
       </c>
@@ -3441,12 +3483,24 @@
       <c r="F39" t="n">
         <v>1.875</v>
       </c>
+      <c r="G39" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.875</v>
+      </c>
       <c r="I39" t="n">
         <v>1.875</v>
       </c>
+      <c r="J39" t="n">
+        <v>0.469</v>
+      </c>
       <c r="K39" t="n">
         <v>1.756</v>
       </c>
+      <c r="L39" t="n">
+        <v>0.125</v>
+      </c>
       <c r="M39" t="n">
         <v>1.312</v>
       </c>
@@ -3463,17 +3517,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: D3@BORE, HEXB@HEX, LEG3@DRIVE, ORB_GRVDIA@DRIVE, Y@REF, THDMAJ_3@DRIVE, D1@BORE, D2@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6803-24-24-24-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21: D3@BORE, HEXB@HEX, LEG3@DRIVE, ORB_GRVDIA@DRIVE, Y@REF, THDMAJ_3@DRIVE, D1@BORE, D2@BORE, LEG1@DRIVE, LEG2@DRIVE, THDMAJ_1@DRIVE, THDMAJ_2@DRIVE, ORB_THDL@DRIVE, ORB_GRVW@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6803-24-24-24-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6803-24-24-24-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6803-24-24-24-NWO-FG (PARTcommunity / CADENAS, D3@BORE=B3D, HEXB@HEX=C, LEG3@DRIVE=M7, ORB_GRVDIA@DRIVE=HT, Y@REF=Y, THDMAJ_3@DRIVE=B3THD, D1@BORE=B1D, D2@BORE=B2D; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6803-24-24-24-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6803-24-24-24-NWO-FG (PARTcommunity / CADENAS, D3@BORE=B3D, HEXB@HEX=C, LEG3@DRIVE=M7, ORB_GRVDIA@DRIVE=HT, Y@REF=Y, THDMAJ_3@DRIVE=B3THD, D1@BORE=B1D, D2@BORE=B2D, LEG1@DRIVE=M1, LEG2@DRIVE=M2, THDMAJ_1@DRIVE=B1THD, THDMAJ_2@DRIVE=B2THD, ORB_THDL@DRIVE=A5, ORB_GRVW@DRIVE=A5; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
